--- a/notepad.xlsx 1.xlsx
+++ b/notepad.xlsx 1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="101">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -286,127 +286,13 @@
     <t>Test the functionality of Windows Notepad Application</t>
   </si>
   <si>
-    <t xml:space="preserve">Notepad Application is open </t>
-  </si>
-  <si>
-    <t>A new blank Notepad file is opened</t>
-  </si>
-  <si>
-    <t>The text size should increase successfully and the content should appear larger</t>
-  </si>
-  <si>
-    <t>The text size should decrease successfully and the content should appear smaller</t>
-  </si>
-  <si>
-    <t>Click on Restore Default Zoom</t>
-  </si>
-  <si>
-    <t>The Zoom level should return to the default 100%</t>
-  </si>
-  <si>
     <t xml:space="preserve">     </t>
-  </si>
-  <si>
-    <t>Long text should automatically move to  the next line without a horizontal scrollbar</t>
-  </si>
-  <si>
-    <t>Click on the status Bar option</t>
-  </si>
-  <si>
-    <t>The status Bar should be displayed at the bottom of the Notepad Window</t>
-  </si>
-  <si>
-    <t>The entered text should be displayed correctly without any errors</t>
-  </si>
-  <si>
-    <t>Select all the entered text using ctrl+A</t>
-  </si>
-  <si>
-    <t>The entire text should be highlighted</t>
-  </si>
-  <si>
-    <t>The selected text should be copied to the clip board sucessfully</t>
-  </si>
-  <si>
-    <t>The copied text should be pasted into the document successfully</t>
-  </si>
-  <si>
-    <t>The last action shouldbe undone successfully</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The previously undone action should be restored </t>
-  </si>
-  <si>
-    <t>The Save As dialog box should open successfully</t>
-  </si>
-  <si>
-    <t>Enter the file name test.text and Click Save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The file should be saved successfully in the selected location </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Close the Notepad application </t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Notepad application should close successfully </t>
   </si>
   <si>
     <t>open the saved test.text file again</t>
   </si>
   <si>
     <t>The saved file should open successfully and all previously entered text should be displayed correctly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search for the Notepad Application </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on the Notepad Application </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that you see this Application icon </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on New Tab </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on the View menu and check the zoom option </t>
-  </si>
-  <si>
-    <t>Make sure that the Zoom menu are available in the View menu</t>
-  </si>
-  <si>
-    <t>Click on the Zoom In option from the View menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on the Zoom Out option from the View menu </t>
-  </si>
-  <si>
-    <t>Click on the Word Wrap option</t>
-  </si>
-  <si>
-    <t>Type a sample paragraph in the Notepad Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on the Copy option </t>
-  </si>
-  <si>
-    <t>Click on the Paste option</t>
-  </si>
-  <si>
-    <t>Click on file-&gt; Save As</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on File menu </t>
-  </si>
-  <si>
-    <t xml:space="preserve">File menu is open then see another tabs </t>
-  </si>
-  <si>
-    <t>Click on the Undo option</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click on the Redo option </t>
   </si>
   <si>
     <t xml:space="preserve">Reviewed By   </t>
@@ -417,6 +303,126 @@
   <si>
     <t xml:space="preserve">Test Case Description </t>
   </si>
+  <si>
+    <t>The saved file should open successfully and all previously entered text should be displayed correctly.</t>
+  </si>
+  <si>
+    <t>The Notepad application should close successfully.</t>
+  </si>
+  <si>
+    <t>The Save As dialog box should open successfully.</t>
+  </si>
+  <si>
+    <t>The previously undone action should be restored.</t>
+  </si>
+  <si>
+    <t>The last action shouldbe undone successfully.</t>
+  </si>
+  <si>
+    <t>The copied text should be pasted into the document successfully.</t>
+  </si>
+  <si>
+    <t>The selected text should be copied to the clip board sucessfully.</t>
+  </si>
+  <si>
+    <t>The entire text should be highlighted.</t>
+  </si>
+  <si>
+    <t>The entered text should be displayed correctly without any errors.</t>
+  </si>
+  <si>
+    <t>The status Bar should be displayed at the bottom of the Notepad Window.</t>
+  </si>
+  <si>
+    <t>Long text should automatically move to  the next line without a horizontal scrollbar.</t>
+  </si>
+  <si>
+    <t>Notepad Application is open.</t>
+  </si>
+  <si>
+    <t>File menu is open then see another tabs.</t>
+  </si>
+  <si>
+    <t>The text size should increase successfully and the content should appear larger.</t>
+  </si>
+  <si>
+    <t>The text size should decrease successfully and the content should appear smaller.</t>
+  </si>
+  <si>
+    <t>open the saved test.text file again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Close the Notepad application. </t>
+  </si>
+  <si>
+    <t>Enter the file name test.text and Click Save.</t>
+  </si>
+  <si>
+    <t>Click on file-&gt; Save As.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click on the Redo option. </t>
+  </si>
+  <si>
+    <t>Click on the Undo option.</t>
+  </si>
+  <si>
+    <t>Click on the Paste option.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click on the Copy option. </t>
+  </si>
+  <si>
+    <t>Type a sample paragraph in the Notepad Document.</t>
+  </si>
+  <si>
+    <t>Click on the status Bar option.</t>
+  </si>
+  <si>
+    <t>Click on the Word Wrap option.</t>
+  </si>
+  <si>
+    <t>Click on Restore Default Zoom.</t>
+  </si>
+  <si>
+    <t>Click on the Zoom Out option from the View menu.</t>
+  </si>
+  <si>
+    <t>Click on File menu.</t>
+  </si>
+  <si>
+    <t>Click on the Notepad Application.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search for the Notepad Application. </t>
+  </si>
+  <si>
+    <t>Click on the View menu and check the zoom option.</t>
+  </si>
+  <si>
+    <t>Click on New Tab.</t>
+  </si>
+  <si>
+    <t>Click on the Zoom In option from the View menu.</t>
+  </si>
+  <si>
+    <t>Select all the entered text using ctrl+A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that you see this Application. icon </t>
+  </si>
+  <si>
+    <t>A new blank Notepad file is opened.</t>
+  </si>
+  <si>
+    <t>Make sure that the Zoom menu are available in the View menu.</t>
+  </si>
+  <si>
+    <t>The Zoom level should return to the default 100%.</t>
+  </si>
+  <si>
+    <t>The file should be saved successfully in the selected. location.</t>
+  </si>
 </sst>
 </file>
 
@@ -425,7 +431,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -470,6 +476,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -895,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -982,49 +995,27 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1036,8 +1027,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1046,14 +1061,54 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1061,66 +1116,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1145,15 +1141,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>263868</xdr:colOff>
+      <xdr:colOff>1003987</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>160897</xdr:rowOff>
+      <xdr:rowOff>180204</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>598529</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>373277</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>360407</xdr:rowOff>
+      <xdr:rowOff>379714</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1170,8 +1166,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2484223" y="2600069"/>
-          <a:ext cx="334661" cy="199510"/>
+          <a:off x="3224342" y="2876809"/>
+          <a:ext cx="399020" cy="199510"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1189,7 +1185,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>946066</xdr:colOff>
+      <xdr:colOff>946065</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>1145576</xdr:rowOff>
     </xdr:to>
@@ -1228,13 +1224,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>128715</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>360406</xdr:rowOff>
+      <xdr:rowOff>450507</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>682196</xdr:colOff>
+      <xdr:colOff>682195</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>2226791</xdr:rowOff>
+      <xdr:rowOff>2168868</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1252,8 +1248,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2349070" y="4427838"/>
-          <a:ext cx="1583210" cy="1866385"/>
+          <a:off x="2349070" y="4775372"/>
+          <a:ext cx="1583210" cy="1718361"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1276,7 +1272,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>926757</xdr:colOff>
+      <xdr:colOff>926756</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>1222803</xdr:rowOff>
     </xdr:to>
@@ -1531,10 +1527,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="46"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1542,13 +1538,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1566,10 +1562,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="41"/>
+      <c r="B2" s="36"/>
       <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1577,14 +1573,14 @@
         <v>6</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="43" t="s">
+      <c r="G2" s="36"/>
+      <c r="H2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="41"/>
+      <c r="I2" s="36"/>
       <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1605,10 +1601,10 @@
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="25.5" customHeight="1">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="41"/>
+      <c r="B3" s="36"/>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1616,14 +1612,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="44">
+      <c r="F3" s="54">
         <v>46220</v>
       </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="43" t="s">
+      <c r="G3" s="36"/>
+      <c r="H3" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="41"/>
+      <c r="I3" s="36"/>
       <c r="J3" s="9" t="s">
         <v>14</v>
       </c>
@@ -1674,21 +1670,21 @@
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="41"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="14"/>
       <c r="F5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="37"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1709,21 +1705,21 @@
       <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="41"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="5"/>
       <c r="F6" s="17">
         <v>1</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="37"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1744,21 +1740,21 @@
       <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="41"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="5"/>
       <c r="F7" s="17">
         <v>2</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="G7" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="46"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="37"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1779,17 +1775,17 @@
       <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="41"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="5"/>
       <c r="F8" s="17">
         <v>3</v>
       </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="37"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1810,17 +1806,17 @@
       <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="50"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="51"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="41"/>
       <c r="K9" s="21"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1868,17 +1864,17 @@
       <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1897,17 +1893,17 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1">
       <c r="A12" s="4"/>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1955,23 +1951,23 @@
       <c r="A14" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="55" t="s">
+      <c r="C14" s="46"/>
+      <c r="D14" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="55" t="s">
+      <c r="E14" s="46"/>
+      <c r="F14" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="55" t="s">
+      <c r="G14" s="47"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="39"/>
+      <c r="J14" s="48"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1992,23 +1988,23 @@
       <c r="A15" s="16">
         <v>1</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="42" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42" t="s">
+      <c r="E15" s="36"/>
+      <c r="F15" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="42" t="s">
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="46"/>
+      <c r="J15" s="37"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -2029,23 +2025,23 @@
       <c r="A16" s="16">
         <v>2</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="45"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="42" t="s">
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="37"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -2066,23 +2062,23 @@
       <c r="A17" s="16">
         <v>3</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42" t="s">
+      <c r="C17" s="36"/>
+      <c r="D17" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42" t="s">
+      <c r="E17" s="36"/>
+      <c r="F17" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="45"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42" t="s">
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="46"/>
+      <c r="J17" s="37"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -2103,23 +2099,23 @@
       <c r="A18" s="16">
         <v>4</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42" t="s">
+      <c r="C18" s="36"/>
+      <c r="D18" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="42" t="s">
+      <c r="E18" s="36"/>
+      <c r="F18" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="45"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="42" t="s">
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="37"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -2140,23 +2136,23 @@
       <c r="A19" s="27">
         <v>5</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42" t="s">
+      <c r="C19" s="36"/>
+      <c r="D19" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="41"/>
-      <c r="F19" s="42" t="s">
+      <c r="E19" s="36"/>
+      <c r="F19" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="45"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="42" t="s">
+      <c r="G19" s="35"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="46"/>
+      <c r="J19" s="37"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2177,23 +2173,23 @@
       <c r="A20" s="27">
         <v>6</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="42" t="s">
+      <c r="C20" s="36"/>
+      <c r="D20" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="42" t="s">
+      <c r="E20" s="36"/>
+      <c r="F20" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="45"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="42" t="s">
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="46"/>
+      <c r="J20" s="37"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2214,23 +2210,23 @@
       <c r="A21" s="27">
         <v>7</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="42" t="s">
+      <c r="C21" s="36"/>
+      <c r="D21" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="42" t="s">
+      <c r="E21" s="36"/>
+      <c r="F21" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="45"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="42" t="s">
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="46"/>
+      <c r="J21" s="37"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2251,23 +2247,23 @@
       <c r="A22" s="27">
         <v>8</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42" t="s">
+      <c r="C22" s="36"/>
+      <c r="D22" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="41"/>
-      <c r="F22" s="42" t="s">
+      <c r="E22" s="36"/>
+      <c r="F22" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="45"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="42" t="s">
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="46"/>
+      <c r="J22" s="37"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2288,15 +2284,15 @@
       <c r="A23" s="27">
         <v>9</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="46"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="37"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2317,15 +2313,15 @@
       <c r="A24" s="27">
         <v>10</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="46"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="37"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2346,15 +2342,15 @@
       <c r="A25" s="27">
         <v>11</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="46"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="37"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2375,15 +2371,15 @@
       <c r="A26" s="27">
         <v>12</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="46"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="37"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2404,15 +2400,15 @@
       <c r="A27" s="27">
         <v>13</v>
       </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="46"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="37"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2433,15 +2429,15 @@
       <c r="A28" s="27">
         <v>14</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="46"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="37"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2462,15 +2458,15 @@
       <c r="A29" s="27">
         <v>15</v>
       </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="46"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="37"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -2491,15 +2487,15 @@
       <c r="A30" s="27">
         <v>16</v>
       </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="46"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="37"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2520,15 +2516,15 @@
       <c r="A31" s="27">
         <v>17</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="46"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="37"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2549,15 +2545,15 @@
       <c r="A32" s="27">
         <v>18</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="46"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="37"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2578,15 +2574,15 @@
       <c r="A33" s="27">
         <v>19</v>
       </c>
-      <c r="B33" s="42"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="46"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="37"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2607,15 +2603,15 @@
       <c r="A34" s="28">
         <v>20</v>
       </c>
-      <c r="B34" s="48"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="51"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="41"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -28554,6 +28550,86 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="B24:C24"/>
@@ -28578,86 +28654,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B15" r:id="rId1"/>
@@ -28672,189 +28668,189 @@
   <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" customWidth="1"/>
     <col min="4" max="5" width="15.42578125" customWidth="1"/>
     <col min="6" max="6" width="5.7109375" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="10" max="10" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="34" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="76" t="s">
-        <v>98</v>
+      <c r="D1" s="63" t="s">
+        <v>60</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="78" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="76" t="s">
-        <v>96</v>
+      <c r="D2" s="63" t="s">
+        <v>58</v>
       </c>
-      <c r="E2" s="78" t="s">
-        <v>97</v>
+      <c r="E2" s="62" t="s">
+        <v>59</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="75" t="s">
+      <c r="G2" s="61"/>
+      <c r="H2" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="71"/>
-      <c r="J2" s="80" t="s">
+      <c r="I2" s="61"/>
+      <c r="J2" s="66" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="78" t="s">
+      <c r="B3" s="61"/>
+      <c r="C3" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="82" t="s">
+      <c r="E3" s="67"/>
+      <c r="F3" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="71"/>
-      <c r="H3" s="75" t="s">
+      <c r="G3" s="61"/>
+      <c r="H3" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="71"/>
-      <c r="J3" s="83" t="s">
+      <c r="I3" s="61"/>
+      <c r="J3" s="69" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="84"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="86" t="s">
+      <c r="B5" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="85" t="s">
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="75" t="s">
+      <c r="G5" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="88">
+      <c r="A6" s="72">
         <v>1</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="88">
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="72">
         <v>1</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="88">
+      <c r="A7" s="72">
         <v>2</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="88">
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="72">
         <v>2</v>
       </c>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="88">
+      <c r="A8" s="72">
         <v>3</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="88">
+      <c r="B8" s="65"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="72">
         <v>3</v>
       </c>
-      <c r="G8" s="70"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="88">
+      <c r="A9" s="72">
         <v>4</v>
       </c>
-      <c r="B9" s="70"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="88">
+      <c r="B9" s="65"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="72">
         <v>4</v>
       </c>
-      <c r="G9" s="70"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="24"/>
@@ -28872,31 +28868,31 @@
       <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="68" t="s">
+      <c r="B11" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="73"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="25"/>
-      <c r="B12" s="69" t="s">
+      <c r="A12" s="32"/>
+      <c r="B12" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" thickBot="1">
       <c r="A13" s="25"/>
@@ -28914,415 +28910,420 @@
       <c r="A14" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="55" t="s">
+      <c r="C14" s="46"/>
+      <c r="D14" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="55" t="s">
+      <c r="E14" s="46"/>
+      <c r="F14" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="55" t="s">
+      <c r="G14" s="47"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="39"/>
+      <c r="J14" s="48"/>
     </row>
     <row r="15" spans="1:10" ht="31.5" customHeight="1">
       <c r="A15" s="27">
         <v>1</v>
       </c>
-      <c r="B15" s="42" t="s">
-        <v>79</v>
+      <c r="B15" s="34" t="s">
+        <v>91</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="42" t="s">
-        <v>81</v>
+      <c r="C15" s="36"/>
+      <c r="D15" s="34" t="s">
+        <v>96</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="46"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="37"/>
     </row>
     <row r="16" spans="1:10" ht="96.75" customHeight="1">
       <c r="A16" s="27">
         <v>2</v>
       </c>
-      <c r="B16" s="42" t="s">
-        <v>80</v>
+      <c r="B16" s="34" t="s">
+        <v>90</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42" t="s">
-        <v>55</v>
+      <c r="C16" s="36"/>
+      <c r="D16" s="34" t="s">
+        <v>72</v>
       </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="46"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="37"/>
     </row>
     <row r="17" spans="1:10" ht="178.5" customHeight="1">
       <c r="A17" s="27">
         <v>3</v>
       </c>
-      <c r="B17" s="42" t="s">
-        <v>92</v>
+      <c r="B17" s="34" t="s">
+        <v>89</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42" t="s">
-        <v>93</v>
+      <c r="C17" s="36"/>
+      <c r="D17" s="34" t="s">
+        <v>73</v>
       </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="46"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="37"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="27">
         <v>4</v>
       </c>
-      <c r="B18" s="42" t="s">
-        <v>82</v>
+      <c r="B18" s="34" t="s">
+        <v>93</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="67" t="s">
-        <v>56</v>
+      <c r="C18" s="36"/>
+      <c r="D18" s="34" t="s">
+        <v>97</v>
       </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="46"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="37"/>
     </row>
     <row r="19" spans="1:10" ht="101.25" customHeight="1">
       <c r="A19" s="27">
         <v>5</v>
       </c>
-      <c r="B19" s="42" t="s">
-        <v>83</v>
+      <c r="B19" s="34" t="s">
+        <v>92</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42" t="s">
-        <v>84</v>
+      <c r="C19" s="36"/>
+      <c r="D19" s="34" t="s">
+        <v>98</v>
       </c>
-      <c r="E19" s="41"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="46"/>
-    </row>
-    <row r="20" spans="1:10" ht="39.75" customHeight="1">
+      <c r="E19" s="36"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="37"/>
+    </row>
+    <row r="20" spans="1:10" ht="47.25" customHeight="1">
       <c r="A20" s="27">
         <v>6</v>
       </c>
-      <c r="B20" s="42" t="s">
-        <v>85</v>
+      <c r="B20" s="34" t="s">
+        <v>94</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="67" t="s">
-        <v>57</v>
+      <c r="C20" s="36"/>
+      <c r="D20" s="34" t="s">
+        <v>74</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="46"/>
-    </row>
-    <row r="21" spans="1:10" ht="43.5" customHeight="1">
+      <c r="E20" s="36"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="37"/>
+    </row>
+    <row r="21" spans="1:10" ht="51.75" customHeight="1">
       <c r="A21" s="27">
         <v>7</v>
       </c>
-      <c r="B21" s="42" t="s">
-        <v>86</v>
+      <c r="B21" s="34" t="s">
+        <v>88</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="67" t="s">
-        <v>58</v>
+      <c r="C21" s="36"/>
+      <c r="D21" s="34" t="s">
+        <v>75</v>
       </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="46"/>
-    </row>
-    <row r="22" spans="1:10" ht="27" customHeight="1">
+      <c r="E21" s="36"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="37"/>
+    </row>
+    <row r="22" spans="1:10" ht="30.75" customHeight="1">
       <c r="A22" s="27">
         <v>8</v>
       </c>
-      <c r="B22" s="42" t="s">
-        <v>59</v>
+      <c r="B22" s="34" t="s">
+        <v>87</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42" t="s">
-        <v>60</v>
+      <c r="C22" s="36"/>
+      <c r="D22" s="34" t="s">
+        <v>99</v>
       </c>
-      <c r="E22" s="41"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="46"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="37"/>
     </row>
     <row r="23" spans="1:10" hidden="1">
-      <c r="A23" s="30" t="s">
-        <v>61</v>
+      <c r="A23" s="74" t="s">
+        <v>55</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="46"/>
-    </row>
-    <row r="24" spans="1:10" ht="44.25" customHeight="1">
+      <c r="B23" s="34"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="37"/>
+    </row>
+    <row r="24" spans="1:10" ht="51.75" customHeight="1">
       <c r="A24" s="27">
         <v>9</v>
       </c>
-      <c r="B24" s="42" t="s">
-        <v>87</v>
+      <c r="B24" s="34" t="s">
+        <v>86</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="42" t="s">
-        <v>62</v>
+      <c r="C24" s="36"/>
+      <c r="D24" s="34" t="s">
+        <v>71</v>
       </c>
-      <c r="E24" s="41"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="46"/>
-    </row>
-    <row r="25" spans="1:10" ht="39" customHeight="1">
+      <c r="E24" s="36"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="37"/>
+    </row>
+    <row r="25" spans="1:10" ht="48" customHeight="1">
       <c r="A25" s="27">
         <v>10</v>
       </c>
-      <c r="B25" s="42" t="s">
-        <v>63</v>
+      <c r="B25" s="34" t="s">
+        <v>85</v>
       </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="42" t="s">
-        <v>64</v>
+      <c r="C25" s="36"/>
+      <c r="D25" s="34" t="s">
+        <v>70</v>
       </c>
-      <c r="E25" s="41"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="46"/>
-    </row>
-    <row r="26" spans="1:10" ht="29.25" customHeight="1">
+      <c r="E25" s="36"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="37"/>
+    </row>
+    <row r="26" spans="1:10" ht="46.5" customHeight="1">
       <c r="A26" s="27">
         <v>11</v>
       </c>
-      <c r="B26" s="42" t="s">
-        <v>88</v>
+      <c r="B26" s="34" t="s">
+        <v>84</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="42" t="s">
-        <v>65</v>
+      <c r="C26" s="36"/>
+      <c r="D26" s="34" t="s">
+        <v>69</v>
       </c>
-      <c r="E26" s="41"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="46"/>
-    </row>
-    <row r="27" spans="1:10" ht="29.25" customHeight="1">
+      <c r="E26" s="36"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="37"/>
+    </row>
+    <row r="27" spans="1:10" ht="35.25" customHeight="1">
       <c r="A27" s="27">
         <v>12</v>
       </c>
-      <c r="B27" s="42" t="s">
-        <v>66</v>
+      <c r="B27" s="34" t="s">
+        <v>95</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42" t="s">
-        <v>67</v>
+      <c r="C27" s="36"/>
+      <c r="D27" s="34" t="s">
+        <v>68</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="46"/>
-    </row>
-    <row r="28" spans="1:10" ht="28.5" customHeight="1">
+      <c r="E27" s="36"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="37"/>
+    </row>
+    <row r="28" spans="1:10" ht="34.5" customHeight="1">
       <c r="A28" s="27">
         <v>13</v>
       </c>
-      <c r="B28" s="42" t="s">
-        <v>89</v>
+      <c r="B28" s="34" t="s">
+        <v>83</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="42" t="s">
-        <v>68</v>
+      <c r="C28" s="36"/>
+      <c r="D28" s="34" t="s">
+        <v>67</v>
       </c>
-      <c r="E28" s="41"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="46"/>
-    </row>
-    <row r="29" spans="1:10" ht="28.5" customHeight="1">
+      <c r="E28" s="36"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="37"/>
+    </row>
+    <row r="29" spans="1:10" ht="33" customHeight="1">
       <c r="A29" s="27">
         <v>14</v>
       </c>
-      <c r="B29" s="42" t="s">
-        <v>90</v>
+      <c r="B29" s="34" t="s">
+        <v>82</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42" t="s">
-        <v>69</v>
+      <c r="C29" s="36"/>
+      <c r="D29" s="34" t="s">
+        <v>66</v>
       </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="46"/>
-    </row>
-    <row r="30" spans="1:10" ht="24.75" customHeight="1">
+      <c r="E29" s="35"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="78"/>
+      <c r="J29" s="37"/>
+    </row>
+    <row r="30" spans="1:10" ht="30" customHeight="1">
       <c r="A30" s="27">
         <v>15</v>
       </c>
-      <c r="B30" s="42" t="s">
-        <v>94</v>
+      <c r="B30" s="34" t="s">
+        <v>81</v>
       </c>
-      <c r="C30" s="41"/>
-      <c r="D30" s="42" t="s">
-        <v>70</v>
+      <c r="C30" s="36"/>
+      <c r="D30" s="34" t="s">
+        <v>65</v>
       </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="46"/>
-    </row>
-    <row r="31" spans="1:10" ht="27" customHeight="1">
+      <c r="E30" s="35"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="37"/>
+    </row>
+    <row r="31" spans="1:10" ht="31.5" customHeight="1">
       <c r="A31" s="27">
         <v>16</v>
       </c>
-      <c r="B31" s="42" t="s">
-        <v>95</v>
+      <c r="B31" s="34" t="s">
+        <v>80</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="42" t="s">
-        <v>71</v>
+      <c r="C31" s="36"/>
+      <c r="D31" s="34" t="s">
+        <v>64</v>
       </c>
-      <c r="E31" s="45"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="46"/>
-    </row>
-    <row r="32" spans="1:10" ht="27" customHeight="1">
+      <c r="E31" s="35"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="37"/>
+    </row>
+    <row r="32" spans="1:10" ht="30" customHeight="1">
       <c r="A32" s="27">
         <v>17</v>
       </c>
-      <c r="B32" s="42" t="s">
-        <v>91</v>
+      <c r="B32" s="34" t="s">
+        <v>79</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="42" t="s">
-        <v>72</v>
+      <c r="C32" s="36"/>
+      <c r="D32" s="34" t="s">
+        <v>63</v>
       </c>
-      <c r="E32" s="45"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="46"/>
-    </row>
-    <row r="33" spans="1:11" ht="27" customHeight="1">
+      <c r="E32" s="35"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="37"/>
+    </row>
+    <row r="33" spans="1:11" ht="32.25" customHeight="1">
       <c r="A33" s="27">
         <v>18</v>
       </c>
-      <c r="B33" s="42" t="s">
-        <v>73</v>
+      <c r="B33" s="34" t="s">
+        <v>78</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="42" t="s">
-        <v>74</v>
+      <c r="C33" s="36"/>
+      <c r="D33" s="34" t="s">
+        <v>100</v>
       </c>
-      <c r="E33" s="45"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="46"/>
-    </row>
-    <row r="34" spans="1:11" ht="27" customHeight="1" thickBot="1">
+      <c r="E33" s="35"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="78"/>
+      <c r="J33" s="37"/>
+    </row>
+    <row r="34" spans="1:11" ht="36.75" customHeight="1" thickBot="1">
       <c r="A34" s="27">
         <v>19</v>
       </c>
-      <c r="B34" s="48" t="s">
-        <v>75</v>
+      <c r="B34" s="38" t="s">
+        <v>77</v>
       </c>
-      <c r="C34" s="50"/>
-      <c r="D34" s="60" t="s">
-        <v>76</v>
+      <c r="C34" s="39"/>
+      <c r="D34" s="38" t="s">
+        <v>62</v>
       </c>
-      <c r="E34" s="49"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="74"/>
-      <c r="J34" s="51"/>
-    </row>
-    <row r="35" spans="1:11" ht="52.5" customHeight="1" thickBot="1">
+      <c r="E34" s="40"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="41"/>
+    </row>
+    <row r="35" spans="1:11" ht="64.5" customHeight="1" thickBot="1">
       <c r="A35" s="27">
         <v>20</v>
       </c>
-      <c r="B35" s="48" t="s">
-        <v>77</v>
+      <c r="B35" s="38" t="s">
+        <v>76</v>
       </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="60" t="s">
-        <v>78</v>
+      <c r="C35" s="39"/>
+      <c r="D35" s="38" t="s">
+        <v>61</v>
       </c>
-      <c r="E35" s="50"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="51"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="82"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="41"/>
     </row>
     <row r="36" spans="1:11" s="29" customFormat="1" ht="47.25" hidden="1" customHeight="1" thickBot="1">
-      <c r="A36" s="32">
+      <c r="A36" s="83">
         <v>21</v>
       </c>
-      <c r="B36" s="61" t="s">
-        <v>77</v>
+      <c r="B36" s="75" t="s">
+        <v>56</v>
       </c>
-      <c r="C36" s="62"/>
-      <c r="D36" s="63" t="s">
-        <v>78</v>
+      <c r="C36" s="77"/>
+      <c r="D36" s="75" t="s">
+        <v>57</v>
       </c>
-      <c r="E36" s="62"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="74"/>
+      <c r="I36" s="74"/>
+      <c r="J36" s="74"/>
     </row>
     <row r="37" spans="1:11" s="29" customFormat="1" ht="27" customHeight="1">
-      <c r="A37" s="31"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
       <c r="D37" s="57"/>
       <c r="E37" s="58"/>
       <c r="F37" s="59"/>
@@ -29330,20 +29331,20 @@
       <c r="H37" s="58"/>
       <c r="I37" s="59"/>
       <c r="J37" s="58"/>
-      <c r="K37" s="31"/>
+      <c r="K37" s="30"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="33"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="31"/>
+      <c r="A38" s="31"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="30"/>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="25"/>
@@ -29407,18 +29408,92 @@
     </row>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
@@ -29435,92 +29510,18 @@
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
